--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4117,6 +4117,113 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128380999</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95718</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hjärtum s, Hjärtum, Boh</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>329309</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6454097</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95718</v>
+        <v>95720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95720</v>
+        <v>95813</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95813</v>
+        <v>95825</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95825</v>
+        <v>95827</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95827</v>
+        <v>95828</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95828</v>
+        <v>95855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95855</v>
+        <v>95868</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>128380999</v>
       </c>
       <c r="B35" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115053840</v>
+        <v>115053873</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329142</v>
+        <v>329179</v>
       </c>
       <c r="R2" t="n">
-        <v>6454007</v>
+        <v>6453827</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115053853</v>
+        <v>115053875</v>
       </c>
       <c r="B3" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329119</v>
+        <v>329315</v>
       </c>
       <c r="R3" t="n">
-        <v>6454197</v>
+        <v>6453741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115053825</v>
+        <v>115053876</v>
       </c>
       <c r="B4" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329400</v>
+        <v>329341</v>
       </c>
       <c r="R4" t="n">
-        <v>6453715</v>
+        <v>6453739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115053841</v>
+        <v>115053810</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>329141</v>
+        <v>329212</v>
       </c>
       <c r="R5" t="n">
-        <v>6453774</v>
+        <v>6454098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1041,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gamla hack</t>
+          <t>Ymnigt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115053804</v>
+        <v>115053811</v>
       </c>
       <c r="B6" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>329367</v>
+        <v>329176</v>
       </c>
       <c r="R6" t="n">
-        <v>6453723</v>
+        <v>6454135</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Allmänt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115053799</v>
+        <v>115053815</v>
       </c>
       <c r="B7" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>329178</v>
+        <v>329085</v>
       </c>
       <c r="R7" t="n">
-        <v>6453985</v>
+        <v>6454219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,15 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115053823</v>
+        <v>115053816</v>
       </c>
       <c r="B8" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>329230</v>
+        <v>329153</v>
       </c>
       <c r="R8" t="n">
-        <v>6453913</v>
+        <v>6454015</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,37 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115053836</v>
+        <v>115053817</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>329198</v>
+        <v>329202</v>
       </c>
       <c r="R9" t="n">
-        <v>6453945</v>
+        <v>6454105</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,37 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115053835</v>
+        <v>115053818</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>329226</v>
+        <v>329214</v>
       </c>
       <c r="R10" t="n">
-        <v>6454021</v>
+        <v>6454111</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,37 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115053831</v>
+        <v>115053819</v>
       </c>
       <c r="B11" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>329120</v>
+        <v>329187</v>
       </c>
       <c r="R11" t="n">
-        <v>6454251</v>
+        <v>6454006</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115053833</v>
+        <v>115053820</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>329102</v>
+        <v>329190</v>
       </c>
       <c r="R12" t="n">
-        <v>6454205</v>
+        <v>6453974</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1726,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,15 +1752,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115053851</v>
+        <v>115053822</v>
       </c>
       <c r="B13" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1843,21 +1763,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>329151</v>
+        <v>329192</v>
       </c>
       <c r="R13" t="n">
-        <v>6454243</v>
+        <v>6453944</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,15 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115053824</v>
+        <v>115053823</v>
       </c>
       <c r="B14" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1969,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>329205</v>
+        <v>329230</v>
       </c>
       <c r="R14" t="n">
-        <v>6453888</v>
+        <v>6453913</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,15 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115053875</v>
+        <v>115053824</v>
       </c>
       <c r="B15" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,21 +1957,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>329315</v>
+        <v>329205</v>
       </c>
       <c r="R15" t="n">
-        <v>6453741</v>
+        <v>6453888</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,37 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115053842</v>
+        <v>115053825</v>
       </c>
       <c r="B16" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>329269</v>
+        <v>329400</v>
       </c>
       <c r="R16" t="n">
-        <v>6453753</v>
+        <v>6453715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2114,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,37 +2140,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115053834</v>
+        <v>115053859</v>
       </c>
       <c r="B17" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>329128</v>
+        <v>329197</v>
       </c>
       <c r="R17" t="n">
-        <v>6454170</v>
+        <v>6454327</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,11 +2211,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,37 +2237,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115053828</v>
+        <v>115053860</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2387,10 +2272,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>329362</v>
+        <v>329085</v>
       </c>
       <c r="R18" t="n">
-        <v>6453724</v>
+        <v>6454219</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2423,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Relativt färska hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,15 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115053800</v>
+        <v>115053861</v>
       </c>
       <c r="B19" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2810</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>329223</v>
+        <v>329178</v>
       </c>
       <c r="R19" t="n">
-        <v>6453896</v>
+        <v>6453780</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,15 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115053819</v>
+        <v>115053793</v>
       </c>
       <c r="B20" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>329187</v>
+        <v>329479</v>
       </c>
       <c r="R20" t="n">
-        <v>6454006</v>
+        <v>6454168</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2658,15 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115053861</v>
+        <v>115053798</v>
       </c>
       <c r="B21" t="n">
-        <v>96283</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,21 +2539,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>329178</v>
+        <v>329212</v>
       </c>
       <c r="R21" t="n">
-        <v>6453780</v>
+        <v>6454098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2760,15 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115053811</v>
+        <v>115053799</v>
       </c>
       <c r="B22" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2776,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>329176</v>
+        <v>329178</v>
       </c>
       <c r="R22" t="n">
-        <v>6454135</v>
+        <v>6453985</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2836,11 +2696,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Allmänt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,15 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115053817</v>
+        <v>115053800</v>
       </c>
       <c r="B23" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>329202</v>
+        <v>329223</v>
       </c>
       <c r="R23" t="n">
-        <v>6454105</v>
+        <v>6453896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,15 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115053852</v>
+        <v>115053804</v>
       </c>
       <c r="B24" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3009,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>329182</v>
+        <v>329367</v>
       </c>
       <c r="R24" t="n">
-        <v>6454139</v>
+        <v>6453723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,15 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115053798</v>
+        <v>128380999</v>
       </c>
       <c r="B25" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3107,17 +2947,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sollum, Boh</t>
+          <t>Hjärtum s, Hjärtum, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>329212</v>
+        <v>329309</v>
       </c>
       <c r="R25" t="n">
-        <v>6454098</v>
+        <v>6454097</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3141,12 +2981,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3161,65 +3011,67 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115053810</v>
+        <v>115101240</v>
       </c>
       <c r="B26" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2569</v>
+        <v>4368</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sollum, Boh</t>
+          <t>Hjärtum s, Hjärtum, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>329212</v>
+        <v>329309</v>
       </c>
       <c r="R26" t="n">
-        <v>6454098</v>
+        <v>6454097</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3243,17 +3095,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ymnigt</t>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3262,33 +3119,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115053822</v>
+        <v>115053828</v>
       </c>
       <c r="B27" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3296,21 +3149,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3320,10 +3173,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>329192</v>
+        <v>329362</v>
       </c>
       <c r="R27" t="n">
-        <v>6453944</v>
+        <v>6453724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,6 +3209,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Relativt färska hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,19 +3240,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115053846</v>
+        <v>115053831</v>
       </c>
       <c r="B28" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3422,10 +3275,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>329160</v>
+        <v>329120</v>
       </c>
       <c r="R28" t="n">
-        <v>6454267</v>
+        <v>6454251</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3462,7 +3315,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3489,15 +3342,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115053876</v>
+        <v>115053833</v>
       </c>
       <c r="B29" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3505,21 +3353,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3529,10 +3377,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>329341</v>
+        <v>329102</v>
       </c>
       <c r="R29" t="n">
-        <v>6453739</v>
+        <v>6454205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3565,6 +3413,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3591,15 +3444,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115053873</v>
+        <v>115053834</v>
       </c>
       <c r="B30" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3607,21 +3455,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3631,10 +3479,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>329179</v>
+        <v>329128</v>
       </c>
       <c r="R30" t="n">
-        <v>6453827</v>
+        <v>6454170</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3667,6 +3515,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3693,15 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115053816</v>
+        <v>115053835</v>
       </c>
       <c r="B31" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3709,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3733,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>329153</v>
+        <v>329226</v>
       </c>
       <c r="R31" t="n">
-        <v>6454015</v>
+        <v>6454021</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3769,6 +3617,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3795,15 +3648,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115053818</v>
+        <v>115053836</v>
       </c>
       <c r="B32" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3811,21 +3659,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3835,10 +3683,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>329214</v>
+        <v>329198</v>
       </c>
       <c r="R32" t="n">
-        <v>6454111</v>
+        <v>6453945</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3871,6 +3719,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3897,15 +3750,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115053820</v>
+        <v>115053840</v>
       </c>
       <c r="B33" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3913,21 +3761,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3937,10 +3785,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>329190</v>
+        <v>329142</v>
       </c>
       <c r="R33" t="n">
-        <v>6453974</v>
+        <v>6454007</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,6 +3821,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3999,60 +3852,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115101240</v>
+        <v>115053841</v>
       </c>
       <c r="B34" t="n">
-        <v>91623</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4368</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hjärtum s, Hjärtum, Boh</t>
+          <t>Sollum, Boh</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>329309</v>
+        <v>329141</v>
       </c>
       <c r="R34" t="n">
-        <v>6454097</v>
+        <v>6453774</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4076,22 +3917,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4100,29 +3936,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingela Eriksson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128380999</v>
+        <v>115053842</v>
       </c>
       <c r="B35" t="n">
-        <v>95879</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,37 +3965,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hjärtum s, Hjärtum, Boh</t>
+          <t>Sollum, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>329309</v>
+        <v>329269</v>
       </c>
       <c r="R35" t="n">
-        <v>6454097</v>
+        <v>6453753</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4184,22 +4019,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:59</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:59</t>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4214,15 +4044,408 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>115053846</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>329160</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6454267</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>115053851</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>329151</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6454243</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>115053852</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>329182</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6454139</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>115053853</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>329119</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6454197</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30285-2025 artfynd.xlsx
+++ b/artfynd/A 30285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053873</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053875</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053876</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053810</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053811</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053815</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053816</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053817</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053818</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053819</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053820</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053822</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053823</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053824</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053825</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053859</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053860</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053861</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053793</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053798</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2719,6 +2824,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053799</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2816,6 +2926,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053800</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2913,6 +3028,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053804</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128380999</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3135,6 +3260,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115101240</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3237,6 +3367,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053828</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3339,6 +3474,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053831</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3441,6 +3581,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053833</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3543,6 +3688,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053834</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3645,6 +3795,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053835</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3747,6 +3902,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053836</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3849,6 +4009,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053840</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3951,6 +4116,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053841</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4053,6 +4223,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053842</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4155,6 +4330,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053846</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4252,6 +4432,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053851</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4349,6 +4534,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053852</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4446,8 +4636,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053853</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>